--- a/Catch models/quantis_btk_conjunto_dbsra.xlsx
+++ b/Catch models/quantis_btk_conjunto_dbsra.xlsx
@@ -393,7 +393,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>0.1426277567198438</v>
+        <v>0.2005942970224689</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -401,7 +401,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>0.3197801868097808</v>
+        <v>0.448216855713191</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -409,7 +409,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>0.4645489866626889</v>
+        <v>0.5683030736113525</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -417,7 +417,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>0.6023610916486027</v>
+        <v>0.6796699116172599</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -425,7 +425,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>0.8452502945905572</v>
+        <v>0.9499687723940016</v>
       </c>
     </row>
   </sheetData>

--- a/Catch models/quantis_btk_conjunto_dbsra.xlsx
+++ b/Catch models/quantis_btk_conjunto_dbsra.xlsx
@@ -393,7 +393,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>0.2005942970224689</v>
+        <v>0.1827374265684944</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -401,7 +401,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>0.448216855713191</v>
+        <v>0.4112545439137484</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -409,7 +409,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>0.5683030736113525</v>
+        <v>0.5100780211333718</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -417,7 +417,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>0.6796699116172599</v>
+        <v>0.7402504054019425</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -425,7 +425,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>0.9499687723940016</v>
+        <v>0.9639141914974089</v>
       </c>
     </row>
   </sheetData>

--- a/Catch models/quantis_btk_conjunto_dbsra.xlsx
+++ b/Catch models/quantis_btk_conjunto_dbsra.xlsx
@@ -393,7 +393,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>0.1827374265684944</v>
+        <v>0.1822753008848551</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -401,7 +401,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>0.4112545439137484</v>
+        <v>0.4157889971100054</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -409,7 +409,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>0.5100780211333718</v>
+        <v>0.5276615457582757</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -417,7 +417,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>0.7402504054019425</v>
+        <v>0.746744723896939</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -425,7 +425,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>0.9639141914974089</v>
+        <v>0.9682194201599084</v>
       </c>
     </row>
   </sheetData>

--- a/Catch models/quantis_btk_conjunto_dbsra.xlsx
+++ b/Catch models/quantis_btk_conjunto_dbsra.xlsx
@@ -393,7 +393,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>0.1822753008848551</v>
+        <v>0.185650845560973</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -401,7 +401,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>0.4157889971100054</v>
+        <v>0.4115397268435367</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -409,7 +409,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>0.5276615457582757</v>
+        <v>0.5271534392896378</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -417,7 +417,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>0.746744723896939</v>
+        <v>0.7466222916525874</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -425,7 +425,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>0.9682194201599084</v>
+        <v>0.964956049232769</v>
       </c>
     </row>
   </sheetData>
